--- a/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
+++ b/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4887,6 +4887,48 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C108" s="8" t="n">
+        <v>3.010724</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>59.267225</v>
+      </c>
+      <c r="E108" s="8" t="n">
+        <v>55.04394</v>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>7.019899</v>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>27 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -4902,7 +4944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8403,6 +8445,38 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>46235</v>
+      </c>
+      <c r="C108" s="12" t="n"/>
+      <c r="D108" s="13" t="n"/>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>27 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>

--- a/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
+++ b/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4929,6 +4929,48 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>2.847999</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>58.451886</v>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>54.290482</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>6.70592</v>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>27 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
@@ -4944,7 +4986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8477,6 +8519,38 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="11" t="n"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>27 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>

--- a/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
+++ b/downloads/indicadores/DESOCUP/DESOCUP_datos.xlsx
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN) · Frecuencia: Mensual · Unidad: porcentaje · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf · Fecha de publicación: 27 de agosto de 2026</t>
+          <t>Fuente: INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN) · Frecuencia: Mensual · Unidad: porcentaje · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf · Fecha de publicación: 22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -594,12 +594,12 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -636,12 +636,12 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,12 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -720,12 +720,12 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2274,12 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3072,12 +3072,12 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3282,12 +3282,12 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3408,12 +3408,12 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3870,12 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4122,12 +4122,12 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4206,12 +4206,12 @@
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4290,12 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4542,12 +4542,12 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4710,12 +4710,12 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4794,12 +4794,12 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN) · Frecuencia: Trimestral · Unidad: millones de personas · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf · Fecha de publicación: 27 de agosto de 2026</t>
+          <t>Fuente: INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN) · Frecuencia: Trimestral · Unidad: millones de personas · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf · Fecha de publicación: 22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5114,12 +5114,12 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5314,12 +5314,12 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5346,12 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5446,12 +5446,12 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5514,12 +5514,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5582,12 +5582,12 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5614,12 +5614,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5682,12 +5682,12 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5946,12 +5946,12 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6214,12 +6214,12 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6246,12 +6246,12 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6282,12 +6282,12 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6446,12 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6482,12 +6482,12 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6514,12 +6514,12 @@
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6546,12 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6682,12 +6682,12 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6714,12 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6814,12 +6814,12 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6846,12 +6846,12 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6946,12 +6946,12 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7014,12 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7046,12 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7082,12 +7082,12 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7114,12 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7246,12 +7246,12 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7282,12 +7282,12 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7346,12 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7382,12 +7382,12 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7582,12 @@
       </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7646,12 +7646,12 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7714,12 +7714,12 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7782,12 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7846,12 +7846,12 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7882,12 +7882,12 @@
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7914,12 +7914,12 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -7982,12 +7982,12 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8046,12 +8046,12 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8182,12 +8182,12 @@
       </c>
       <c r="G98" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8214,12 +8214,12 @@
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8282,12 +8282,12 @@
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8314,12 +8314,12 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8414,12 +8414,12 @@
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8510,12 +8510,12 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_08.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/iooe/IOE2026_10.pdf</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>27 de agosto de 2026</t>
+          <t>22 de octubre de 2026</t>
         </is>
       </c>
     </row>
